--- a/DataTD3.xlsx
+++ b/DataTD3.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\33695\Desktop\Cours VBA Master 1\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{079BF23C-BA48-4B5A-B000-7E433A54F9E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{82C06A57-001E-4087-B549-98120C71EEC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{2D6F8EE2-35C6-4E26-94E9-CB41A3FEDA04}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{2D6F8EE2-35C6-4E26-94E9-CB41A3FEDA04}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Yield" sheetId="2" r:id="rId2"/>
   </sheets>
   <externalReferences>
     <externalReference r:id="rId3"/>
@@ -161,6 +161,55 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>542925</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>220561</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>38579</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6CC7D11E-8A93-20A7-27C8-91BF1604B35E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3952875" y="609600"/>
+          <a:ext cx="10650436" cy="3429479"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
@@ -173,7 +222,7 @@
       <sheetName val="Summary"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1"/>
       <sheetData sheetId="2"/>
     </sheetDataSet>
@@ -16213,5 +16262,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>